--- a/human_validation/judge/kor/judge_D018_S005_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D018_S005_P003__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,103 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 앉으세요. 오늘 저를 찾아오시게 된 이유가 무엇인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 주로 요즘 잠을 제대로 못 자서 왔어요. 오랫동안 깨어 있다가, 나쁜 꿈이나 심지어 작은 소리에도 깨서 다시 잠들지 못하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 수면 문제가 특별히 스트레스가 되거나 무서웠던 사건 이후에 시작됐나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네. 사다리에서 떨어진 후에 시작됐어요 — 이제 한 1년 7개월쯤 전이네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 적응장애 (D020) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 낮에 그 추락에 대한 원치 않는 기억이나 이미지가 불쑥 떠오르나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 가끔 그래요. 금속이 긁히는 소리를 듣거나, 누군가의 마당에 사다리가 기대어 있는 걸 보면, 그게 한꺼번에 다시 돌아와요. 그 밑에 다시 깔려 있는 것 같아요, 누가 도와주러 오길 기다리면서요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 적응장애 (D020) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 추락을 떠올리게 하는 장소나 활동, 사람들을 피하려고 하시는 걸 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네. 노인 센터에 안 갈 핑계를 계속 찾게 되고, 차고 근처에서 작업하는 것도 피해요 — 특히 공구들이랑 예전에 그 사다리를 보관하던 자리 근처요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 적응장애 (D020) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>진단명: 외상후 스트레스장애 (D018)
 인구통계: 성별 남성 / 나이 74 / 직업상태 not in workforce / 최종학력 중학교 중퇴 이하
@@ -575,170 +663,45 @@
 증상 지속 기간: 1 year and 7 months
 추가 요건: 
 주호소 증상 코드: S027
-배경 서술: 제시의 심각한 개인 부상은 노인 센터에서 장식품 수리를 돕던 중 사다리가 무너지면서 발생했고, 그는 심하게 다친 채 이웃과 응급 대원들이 도착할 때까지 잠시 갇혀 있었다. 그 후 1년 7개월 동안, 그의 회복은 신체적으로는 충분한 것처럼 보였지만, 그는 점차 공구 작업과 노인 센터, 심지어 자신의 차고 일부까지 피하게 되었다. 한편 침투적인 회상, 충격을 받은 순간에 대한 기억의 공백, 나빠진 수면, 일상적인 안전에 대해 더 의심하는 태도, 아내와 브리지 게임 친구들과의 정서적 거리감, 정원 가꾸기와 라디오 복원에 대한 즐거움 감소, 짜증, 과도한 경계심, 갑작스러운 소리에 대한 놀람 반응이 눈에 띄지만 제한적인 정도의 지장을 일으켰다. 그는 부상에 대한 정기 후속 진료 중 이런 변화들을 언급한 후 정신과 진료를 받게 되었는데, 당시 담당 의사는 이미 회복된 골절에 비해 외상과 관련된 이 지속적인 패턴이 과도하다는 걸 알아채고 그를 평가로 의뢰했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 앉으세요. 오늘 저를 찾아오시게 된 이유가 무엇인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 주로 요즘 잠을 제대로 못 자서 왔어요. 오랫동안 깨어 있다가, 나쁜 꿈이나 심지어 작은 소리에도 깨서 다시 잠들지 못하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 수면 문제가 특별히 스트레스가 되거나 무서웠던 사건 이후에 시작됐나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네. 사다리에서 떨어진 후에 시작됐어요 — 이제 한 1년 7개월쯤 전이네요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 낮에 그 추락에 대한 원치 않는 기억이나 이미지가 불쑥 떠오르나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 가끔 그래요. 금속이 긁히는 소리를 듣거나, 누군가의 마당에 사다리가 기대어 있는 걸 보면, 그게 한꺼번에 다시 돌아와요. 그 밑에 다시 깔려 있는 것 같아요, 누가 도와주러 오길 기다리면서요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 추락을 떠올리게 하는 장소나 활동, 사람들을 피하려고 하시는 걸 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네. 노인 센터에 안 갈 핑계를 계속 찾게 되고, 차고 근처에서 작업하는 것도 피해요 — 특히 공구들이랑 예전에 그 사다리를 보관하던 자리 근처요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+배경 서술: 제시의 심각한 개인 부상은 노인 센터에서 장식품 수리를 돕던 중 사다리가 무너지면서 발생했고, 그는 심하게 다친 채 이웃과 응급 대원들이 도착할 때까지 잠시 갇혀 있었다. 그 후 1년 7개월 동안, 그의 회복은 신체적으로는 충분한 것처럼 보였지만, 그는 점차 공구 작업과 노인 센터, 심지어 자신의 차고 일부까지 피하게 되었다. 한편 침투적인 회상, 충격을 받은 순간에 대한 기억의 공백, 나빠진 수면, 일상적인 안전에 대해 더 의심하는 태도, 아내와 브리지 게임 친구들과의 정서적 거리감, 정원 가꾸기와 라디오 복원에 대한 즐거움 감소, 짜증, 과도한 경계심, 갑작스러운 소리에 대한 놀람 반응이 눈에 띄지만 제한적인 정도의 지장을 일으켰다. 그는 부상에 대한 정기 후속 진료 중 이런 변화들을 언급한 후 정신과 진료를 받게 되었는데, 당시 담당 의사는 이미 회복된 골절에 비해 외상과 관련된 이 지속적인 패턴이 과도하다는 걸 알아채고 그를 평가로 의뢰했다.
+표집된 증상 목록:
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S069 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.
+  - S070 외상 관련 회피: 외상 사건과 관련된 자극을 지속적으로 회피함.
+  - S071 외상 관련 기억상실: 외상 사건의 중요한 부분을 기억하지 못함(통상 해리성 기억상실에 의한 것으로, 두부 손상이나 알코올 등 다른 요인에 의한 것이 아님).
+  - S072 부정적 신념: 자신, 타인, 세상에 대한 지속적이고 과장된 부정적 믿음이나 기대.
+  - S075 사회적 유리감: 타인으로부터 동떨어지거나 소외된 느낌.
+  - S076 긍정적 정서 표현 불능: 긍정적 정서를 지속적으로 경험하지 못함(예: 행복, 만족, 애정을 느끼지 못함).
+  - S077 과민성/공격성: 사소하거나 별다른 도발 없이도 언어적·신체적 공격성으로 나타나는 과민한 행동과 분노 폭발.
+  - S079 과각성: 주변 환경에 대해 지속적으로 경계하고 긴장하는 상태.
+  - S080 과장된 놀람 반응: 사소한 자극에도 과장되게 놀라는 반응.</t>
+        </is>
+      </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 외상후 스트레스장애 (D018, ICD: F43.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: trauma_related_symptoms (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.; 외상 관련 회피: 외상 사건과 관련된 자극을 지속적으로 회피함.
-  누락: (없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: trauma_related_alterations (관계=must_include, 요구개수=2, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 외상 관련 기억상실: 외상 사건의 중요한 부분을 기억하지 못함(통상 해리성 기억상실에 의한 것으로, 두부 손상이나 알코올 등 다른 요인에 의한 것이 아님).; 부정적 신념: 자신, 타인, 세상에 대한 지속적이고 과장된 부정적 믿음이나 기대.; 왜곡된 인지와 비난: 외상 사건의 원인이나 결과에 대해 지속적이고 왜곡된 인지를 가지고 있어 자신이나 타인을 비난하게 됨.; 지속적인 부정적 정서 상태: 지속적인 부정적 정서 상태(예: 두려움, 공포, 분노, 죄책감, 수치심).; 사회적 유리감: 타인으로부터 동떨어지거나 소외된 느낌.; 긍정적 정서 표현 불능: 긍정적 정서를 지속적으로 경험하지 못함(예: 행복, 만족, 애정을 느끼지 못함).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: arousal_and_reactivity (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
-  확인된 근거: 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
-  누락: 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 과민성/공격성: 사소하거나 별다른 도발 없이도 언어적·신체적 공격성으로 나타나는 과민한 행동과 분노 폭발.; 무모/자기파괴적 행동: 자신의 안전이나 건강을 위태롭게 하는 무모하거나 자기파괴적인 행동 양상.; 과각성: 주변 환경에 대해 지속적으로 경계하고 긴장하는 상태.; 과장된 놀람 반응: 사소한 자극에도 과장되게 놀라는 반응.</t>
+          <t>의사의 최종 진단: 외상후 스트레스장애 (D018, ICD: F43.1)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: trauma_related_symptoms (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.
+  - 외상 관련 회피: 외상 사건과 관련된 자극을 지속적으로 회피함.
+체크리스트 그룹: trauma_related_alterations (관계=must_include, 요구개수=2, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)
+체크리스트 그룹: arousal_and_reactivity (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
+확인된 근거:
+  - 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D018_S005_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D018_S005_P003__gemini-3.8-flash_kor.xlsx
@@ -649,6 +649,11 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -697,11 +702,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D018_S005_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D018_S005_P003__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1667</v>
+        <v>0.3958</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.9375</v>
+        <v>0.7708</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1723</v>
+        <v>0.4688</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.8333</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
